--- a/Proyecto Interno/interno/02_dataprep/eer/output/230726_adult_eer.xlsx
+++ b/Proyecto Interno/interno/02_dataprep/eer/output/230726_adult_eer.xlsx
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>24.41624565374147</v>
+        <v>24.39043752001584</v>
       </c>
       <c r="E7">
-        <v>72.26497357501798</v>
+        <v>72.14816748211379</v>
       </c>
       <c r="F7">
-        <v>170.5232202851548</v>
+        <v>171.0258019352922</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="I7">
-        <v>3001.939185407725</v>
+        <v>3003.637134916764</v>
       </c>
     </row>
     <row r="8">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>39.87517445850919</v>
+        <v>39.8841702557612</v>
       </c>
       <c r="E8">
-        <v>77.66854476045276</v>
+        <v>77.83004059257166</v>
       </c>
       <c r="F8">
-        <v>169.9800024605575</v>
+        <v>170.2167379767821</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="I8">
-        <v>2916.948023795984</v>
+        <v>2920.96351356654</v>
       </c>
     </row>
     <row r="9">
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="D19">
-        <v>24.48751767793022</v>
+        <v>24.49851620563767</v>
       </c>
       <c r="E19">
-        <v>60.95317531041974</v>
+        <v>60.96976992721736</v>
       </c>
       <c r="F19">
-        <v>156.9932498128257</v>
+        <v>157.4464224105097</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="I19">
-        <v>2180.239498110854</v>
+        <v>2183.354796224263</v>
       </c>
     </row>
     <row r="20">
@@ -1159,13 +1159,13 @@
         </is>
       </c>
       <c r="D21">
-        <v>56.84911835574319</v>
+        <v>56.84886414345694</v>
       </c>
       <c r="E21">
-        <v>66.45090228505011</v>
+        <v>66.43060141483755</v>
       </c>
       <c r="F21">
-        <v>154.1425422751909</v>
+        <v>154.3759650788053</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="I21">
-        <v>2139.834041003507</v>
+        <v>2141.111895428849</v>
       </c>
     </row>
     <row r="22">
@@ -1237,13 +1237,13 @@
         </is>
       </c>
       <c r="D23">
-        <v>24.43664919521046</v>
+        <v>24.40882460615636</v>
       </c>
       <c r="E23">
-        <v>70.91661700355833</v>
+        <v>71.25988410453083</v>
       </c>
       <c r="F23">
-        <v>169.0878771154904</v>
+        <v>169.7558979792874</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="I23">
-        <v>2970.907424535481</v>
+        <v>2981.025640443366</v>
       </c>
     </row>
     <row r="24">
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="D24">
-        <v>40.00591693919979</v>
+        <v>39.99832445085037</v>
       </c>
       <c r="E24">
-        <v>75.5342120871304</v>
+        <v>75.53636814946717</v>
       </c>
       <c r="F24">
-        <v>168.3945709627751</v>
+        <v>168.5715375993396</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="I24">
-        <v>2871.237836532005</v>
+        <v>2872.508188603007</v>
       </c>
     </row>
     <row r="25">
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="D27">
-        <v>24.68388398634215</v>
+        <v>24.67914563433931</v>
       </c>
       <c r="E27">
-        <v>62.95894766538862</v>
+        <v>62.98184149244761</v>
       </c>
       <c r="F27">
-        <v>157.3929810627744</v>
+        <v>157.7032976915605</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="I27">
-        <v>2205.851272927871</v>
+        <v>2208.210509585895</v>
       </c>
     </row>
     <row r="28">
@@ -1978,13 +1978,13 @@
         </is>
       </c>
       <c r="D42">
-        <v>15.98828619141133</v>
+        <v>15.98828915410318</v>
       </c>
       <c r="E42">
-        <v>53.943005507317</v>
+        <v>53.94275574289637</v>
       </c>
       <c r="F42">
-        <v>156.8782493370188</v>
+        <v>156.8886758124459</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="I42">
-        <v>2164.636347397608</v>
+        <v>2164.765748539002</v>
       </c>
     </row>
     <row r="43">
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="D43">
-        <v>24.40294711144092</v>
+        <v>24.40323479302869</v>
       </c>
       <c r="E43">
-        <v>61.79354577728078</v>
+        <v>61.78803894127606</v>
       </c>
       <c r="F43">
-        <v>156.8919853122076</v>
+        <v>156.9606883020158</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="I43">
-        <v>2190.366089545558</v>
+        <v>2190.750659641264</v>
       </c>
     </row>
     <row r="44">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="D44">
-        <v>40.08078336034185</v>
+        <v>40.0817248026233</v>
       </c>
       <c r="E44">
-        <v>66.90258189091377</v>
+        <v>66.90890378007293</v>
       </c>
       <c r="F44">
-        <v>155.8349860588426</v>
+        <v>155.8624421603502</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="I44">
-        <v>2135.511960788058</v>
+        <v>2135.763319282007</v>
       </c>
     </row>
     <row r="45">
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="D45">
-        <v>54.80085059568864</v>
+        <v>54.79921847264416</v>
       </c>
       <c r="E45">
-        <v>66.74349163022856</v>
+        <v>66.55047853699979</v>
       </c>
       <c r="F45">
-        <v>154.0433255198046</v>
+        <v>153.9520355804043</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="I45">
-        <v>2018.567974145908</v>
+        <v>2015.63372277661</v>
       </c>
     </row>
     <row r="46">
@@ -2134,13 +2134,13 @@
         </is>
       </c>
       <c r="D46">
-        <v>77.59464596863614</v>
+        <v>76.94760596546311</v>
       </c>
       <c r="E46">
-        <v>82.57500396008237</v>
+        <v>59.77825745682888</v>
       </c>
       <c r="F46">
-        <v>269.9147790274038</v>
+        <v>150.0459183673469</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I46">
-        <v>2950.529735466498</v>
+        <v>1889.811285321821</v>
       </c>
     </row>
     <row r="47">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="D47">
-        <v>15.986115154565</v>
+        <v>15.98610917373326</v>
       </c>
       <c r="E47">
-        <v>58.25724051790883</v>
+        <v>58.25769591927926</v>
       </c>
       <c r="F47">
-        <v>166.5562043365584</v>
+        <v>166.5980539136914</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="I47">
-        <v>2715.120222853123</v>
+        <v>2715.490179738342</v>
       </c>
     </row>
     <row r="48">
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="D48">
-        <v>24.34593941248654</v>
+        <v>24.34245212560843</v>
       </c>
       <c r="E48">
-        <v>70.07845345943031</v>
+        <v>70.00879053420226</v>
       </c>
       <c r="F48">
-        <v>169.4276088195669</v>
+        <v>169.4970643700773</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="I48">
-        <v>2960.769680205883</v>
+        <v>2960.151960571723</v>
       </c>
     </row>
     <row r="49">
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="D49">
-        <v>40.01133172090937</v>
+        <v>40.01175517192909</v>
       </c>
       <c r="E49">
-        <v>75.27558966178262</v>
+        <v>75.28246094552111</v>
       </c>
       <c r="F49">
-        <v>168.2117479780532</v>
+        <v>168.2799707869225</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="I49">
-        <v>2865.87250579842</v>
+        <v>2866.422054661984</v>
       </c>
     </row>
     <row r="50">
@@ -2290,13 +2290,13 @@
         </is>
       </c>
       <c r="D50">
-        <v>54.81586335316391</v>
+        <v>54.81375469447809</v>
       </c>
       <c r="E50">
-        <v>74.01074629189138</v>
+        <v>73.98006400082097</v>
       </c>
       <c r="F50">
-        <v>166.4125571742388</v>
+        <v>166.3315814171955</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="I50">
-        <v>2673.685046165263</v>
+        <v>2672.691765751979</v>
       </c>
     </row>
     <row r="51">
@@ -2329,13 +2329,13 @@
         </is>
       </c>
       <c r="D51">
-        <v>77.43927755864647</v>
+        <v>76.9878844361603</v>
       </c>
       <c r="E51">
-        <v>83.42204691716836</v>
+        <v>65.37162162162163</v>
       </c>
       <c r="F51">
-        <v>227.8775171268424</v>
+        <v>161.8576421248835</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="I51">
-        <v>2979.15880215902</v>
+        <v>2266.415538210625</v>
       </c>
     </row>
     <row r="52">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="D53">
-        <v>24.48751767793022</v>
+        <v>24.49851620563767</v>
       </c>
       <c r="E53">
-        <v>60.95317531041974</v>
+        <v>60.96976992721736</v>
       </c>
       <c r="F53">
-        <v>156.9932498128257</v>
+        <v>157.4464224105097</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="I53">
-        <v>2180.239498110854</v>
+        <v>2183.354796224263</v>
       </c>
     </row>
     <row r="54">
@@ -2485,13 +2485,13 @@
         </is>
       </c>
       <c r="D55">
-        <v>56.84911835574319</v>
+        <v>56.84886414345694</v>
       </c>
       <c r="E55">
-        <v>66.45090228505011</v>
+        <v>66.43060141483755</v>
       </c>
       <c r="F55">
-        <v>154.1425422751909</v>
+        <v>154.3759650788053</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="I55">
-        <v>2139.834041003507</v>
+        <v>2141.111895428849</v>
       </c>
     </row>
     <row r="56">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="D57">
-        <v>24.43664919521046</v>
+        <v>24.40882460615636</v>
       </c>
       <c r="E57">
-        <v>70.91661700355833</v>
+        <v>71.25988410453083</v>
       </c>
       <c r="F57">
-        <v>169.0878771154904</v>
+        <v>169.7558979792874</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="I57">
-        <v>2970.907424535481</v>
+        <v>2981.025640443366</v>
       </c>
     </row>
     <row r="58">
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="D58">
-        <v>40.00591693919979</v>
+        <v>39.99832445085037</v>
       </c>
       <c r="E58">
-        <v>75.5342120871304</v>
+        <v>75.53636814946717</v>
       </c>
       <c r="F58">
-        <v>168.3945709627751</v>
+        <v>168.5715375993396</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I58">
-        <v>2871.237836532005</v>
+        <v>2872.508188603007</v>
       </c>
     </row>
     <row r="59">
@@ -2719,13 +2719,13 @@
         </is>
       </c>
       <c r="D61">
-        <v>24.33476177756792</v>
+        <v>24.33060984770631</v>
       </c>
       <c r="E61">
-        <v>62.67985103044771</v>
+        <v>62.67113103245102</v>
       </c>
       <c r="F61">
-        <v>156.5426194677335</v>
+        <v>156.6225936014818</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="I61">
-        <v>2199.297999935925</v>
+        <v>2199.749073471314</v>
       </c>
     </row>
     <row r="62">
@@ -2758,13 +2758,13 @@
         </is>
       </c>
       <c r="D62">
-        <v>40.2268733563928</v>
+        <v>40.23164607702204</v>
       </c>
       <c r="E62">
-        <v>66.33500633356715</v>
+        <v>66.34164021356742</v>
       </c>
       <c r="F62">
-        <v>154.5406873145943</v>
+        <v>154.5881661950555</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="I62">
-        <v>2119.055130937514</v>
+        <v>2119.41557008015</v>
       </c>
     </row>
     <row r="63">
@@ -2836,13 +2836,13 @@
         </is>
       </c>
       <c r="D64">
-        <v>15.88302730022283</v>
+        <v>15.88232227315079</v>
       </c>
       <c r="E64">
-        <v>59.17833294986018</v>
+        <v>59.1902569140827</v>
       </c>
       <c r="F64">
-        <v>165.7507400002148</v>
+        <v>166.3314727715403</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="I64">
-        <v>2726.477511489837</v>
+        <v>2731.722651473469</v>
       </c>
     </row>
     <row r="65">
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="D66">
-        <v>39.94328221962337</v>
+        <v>39.95969815345145</v>
       </c>
       <c r="E66">
-        <v>74.25872882741723</v>
+        <v>74.24867127598179</v>
       </c>
       <c r="F66">
-        <v>167.1282818939718</v>
+        <v>167.396283613588</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="I66">
-        <v>2843.367027154383</v>
+        <v>2844.776598159585</v>
       </c>
     </row>
     <row r="67">
@@ -3226,13 +3226,13 @@
         </is>
       </c>
       <c r="D74">
-        <v>40.33093655669853</v>
+        <v>40.32943971388972</v>
       </c>
       <c r="E74">
-        <v>73.06272619347838</v>
+        <v>73.06492986807928</v>
       </c>
       <c r="F74">
-        <v>168.0260812128475</v>
+        <v>168.043421270221</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I74">
-        <v>2825.993980336962</v>
+        <v>2826.158308781556</v>
       </c>
     </row>
     <row r="75">
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="D78">
-        <v>40.02649194169766</v>
+        <v>40.03332080689106</v>
       </c>
       <c r="E78">
-        <v>65.6379266223105</v>
+        <v>65.64805455355187</v>
       </c>
       <c r="F78">
-        <v>156.6429520047366</v>
+        <v>156.7333120142798</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="I78">
-        <v>2125.872203914811</v>
+        <v>2126.54366271806</v>
       </c>
     </row>
     <row r="79">
@@ -3421,13 +3421,13 @@
         </is>
       </c>
       <c r="D79">
-        <v>56.92483235507802</v>
+        <v>56.92793339252522</v>
       </c>
       <c r="E79">
-        <v>66.81997009780123</v>
+        <v>66.83059371608798</v>
       </c>
       <c r="F79">
-        <v>154.2958412077394</v>
+        <v>154.4066323496997</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="I79">
-        <v>2006.27391414929</v>
+        <v>2007.112368139724</v>
       </c>
     </row>
     <row r="80">
@@ -3499,13 +3499,13 @@
         </is>
       </c>
       <c r="D81">
-        <v>24.37490486917048</v>
+        <v>24.3702710132358</v>
       </c>
       <c r="E81">
-        <v>72.39755794607181</v>
+        <v>71.36560925067869</v>
       </c>
       <c r="F81">
-        <v>170.2606007338943</v>
+        <v>170.2804781093562</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="I81">
-        <v>3002.784043973877</v>
+        <v>2986.545525377957</v>
       </c>
     </row>
     <row r="82">
@@ -3616,13 +3616,13 @@
         </is>
       </c>
       <c r="D84">
-        <v>15.85371444104909</v>
+        <v>15.85436854945243</v>
       </c>
       <c r="E84">
-        <v>53.37563310281693</v>
+        <v>53.37722343441909</v>
       </c>
       <c r="F84">
-        <v>156.9316096849535</v>
+        <v>157.0079465371843</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="I84">
-        <v>2159.954584968008</v>
+        <v>2160.93827824352</v>
       </c>
     </row>
     <row r="85">
@@ -3655,13 +3655,13 @@
         </is>
       </c>
       <c r="D85">
-        <v>24.13001342559792</v>
+        <v>24.13131469338091</v>
       </c>
       <c r="E85">
-        <v>60.62164920772616</v>
+        <v>60.51779796155986</v>
       </c>
       <c r="F85">
-        <v>156.77018753997</v>
+        <v>156.9538177940534</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="I85">
-        <v>2314.446783621303</v>
+        <v>2314.357079218158</v>
       </c>
     </row>
     <row r="86">
@@ -3694,13 +3694,13 @@
         </is>
       </c>
       <c r="D86">
-        <v>39.89350935450409</v>
+        <v>39.8851833317148</v>
       </c>
       <c r="E86">
-        <v>67.42088364687915</v>
+        <v>67.41176120883486</v>
       </c>
       <c r="F86">
-        <v>156.7844609159015</v>
+        <v>156.9085504991137</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="I86">
-        <v>2287.940578017411</v>
+        <v>2288.697918425905</v>
       </c>
     </row>
     <row r="87">
@@ -3850,13 +3850,13 @@
         </is>
       </c>
       <c r="D90">
-        <v>40.38820877163747</v>
+        <v>40.38387658435556</v>
       </c>
       <c r="E90">
-        <v>75.06552024243794</v>
+        <v>75.05851782729818</v>
       </c>
       <c r="F90">
-        <v>168.4765854594249</v>
+        <v>168.6299518981785</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="I90">
-        <v>2860.175463255805</v>
+        <v>2861.110921599867</v>
       </c>
     </row>
     <row r="91">
@@ -3889,13 +3889,13 @@
         </is>
       </c>
       <c r="D91">
-        <v>56.82793644083099</v>
+        <v>56.82308321507102</v>
       </c>
       <c r="E91">
-        <v>72.87470790676771</v>
+        <v>72.88791496313813</v>
       </c>
       <c r="F91">
-        <v>167.2866614229048</v>
+        <v>167.371288423988</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="I91">
-        <v>2639.519083619814</v>
+        <v>2640.33353636871</v>
       </c>
     </row>
     <row r="92">
@@ -4006,13 +4006,13 @@
         </is>
       </c>
       <c r="D94">
-        <v>39.99113874047401</v>
+        <v>39.99183155672517</v>
       </c>
       <c r="E94">
-        <v>64.12755777460609</v>
+        <v>64.12964562171686</v>
       </c>
       <c r="F94">
-        <v>152.3815361934992</v>
+        <v>152.3951944124903</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="I94">
-        <v>2079.65880769009</v>
+        <v>2079.769441757435</v>
       </c>
     </row>
     <row r="95">
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="D98">
-        <v>39.78621609858459</v>
+        <v>39.79334427320679</v>
       </c>
       <c r="E98">
-        <v>70.30903852180953</v>
+        <v>70.30920149475305</v>
       </c>
       <c r="F98">
-        <v>164.4381452047768</v>
+        <v>164.6467119041361</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I98">
-        <v>2764.688789269463</v>
+        <v>2765.974038917659</v>
       </c>
     </row>
     <row r="99">
@@ -4474,13 +4474,13 @@
         </is>
       </c>
       <c r="D106">
-        <v>40.33093655669853</v>
+        <v>40.32943971388972</v>
       </c>
       <c r="E106">
-        <v>73.06272619347838</v>
+        <v>73.06492986807928</v>
       </c>
       <c r="F106">
-        <v>168.0260812128475</v>
+        <v>168.043421270221</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I106">
-        <v>2825.993980336962</v>
+        <v>2826.158308781556</v>
       </c>
     </row>
     <row r="107">
@@ -4552,13 +4552,13 @@
         </is>
       </c>
       <c r="D108">
-        <v>16.21212196183992</v>
+        <v>16.211807614667</v>
       </c>
       <c r="E108">
-        <v>53.64164235478848</v>
+        <v>53.64353417280729</v>
       </c>
       <c r="F108">
-        <v>155.281076468609</v>
+        <v>155.3227223766109</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="I108">
-        <v>2134.821024739233</v>
+        <v>2135.387703688431</v>
       </c>
     </row>
     <row r="109">
@@ -4630,13 +4630,13 @@
         </is>
       </c>
       <c r="D110">
-        <v>39.77897647387753</v>
+        <v>39.77874143718699</v>
       </c>
       <c r="E110">
-        <v>66.49750653347405</v>
+        <v>66.49709953539482</v>
       </c>
       <c r="F110">
-        <v>153.710204542364</v>
+        <v>153.7189656088192</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="I110">
-        <v>2118.686454214096</v>
+        <v>2118.740983903219</v>
       </c>
     </row>
     <row r="111">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="D111">
-        <v>56.16307991009592</v>
+        <v>56.16430459759481</v>
       </c>
       <c r="E111">
-        <v>64.84718769562184</v>
+        <v>64.82270319692476</v>
       </c>
       <c r="F111">
-        <v>151.2055136396246</v>
+        <v>151.3156600395047</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="I111">
-        <v>1967.268058476599</v>
+        <v>1967.689197842258</v>
       </c>
     </row>
     <row r="112">
